--- a/astro-site/public/dl/hotel-checklist-templates/09-hotel-housekeeping-checklists.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/09-hotel-housekeeping-checklists.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Strip all bed linen: sheets, pillowcases, pillows; check mattress seams and box spring for bed bugs and tell your supervisor if you see anything</t>
+          <t>Strip all bed linen: sheets, pillowcases and pillow protectors; check mattress seams and box spring for bed bugs and tell your supervisor if you see anything</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Polish floors (hardwood, marble, carpet per material)</t>
+          <t>Polish hard floors (hardwood, marble) and shampoo or hot-water-extract carpet, per material</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
